--- a/daily_matches/job_matches_2026-03-20.xlsx
+++ b/daily_matches/job_matches_2026-03-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>QA Engineer</t>
+          <t>Software Engineer III - Virtual Agent</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>AccuLynx</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Beloit, WI, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Jenkins, Git, SQL, R, Java</t>
+          <t>Generative AI, RAG, S3, CI/CD, Terraform, Git, Kafka, Python, SQL, R</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,102 +496,102 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c0febea5d0bcbf0</t>
+          <t>https://www.indeed.com/viewjob?jk=eae9a81ad22115c8</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1154_Sr Systems Administrator (Power Platform/Azure)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>LATCH LLC</t>
+          <t>TELEWORLD SOLUTIONS INC</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chantilly, VA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, R</t>
+          <t>Generative AI, RAG, Docker, Kubernetes, CI/CD, Terraform, PostgreSQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b5f97a66bbda7bc</t>
+          <t>https://www.indeed.com/viewjob?jk=9a761aeedea031f5</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Oracle DBA - OCI</t>
+          <t>Global Services Data Scientist - Senior Associate</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Snowflake, Cassandra, NoSQL, SQL, R, Scala, Optimization</t>
+          <t>Data Scientist, RAG, Cortex, Snowflake, Databricks, Hadoop, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e599db25edc63644</t>
+          <t>https://www.indeed.com/viewjob?jk=dc1e4dcc78fd61e0</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Oracle DBA - OCI</t>
+          <t>Senior Data &amp; AI Platform Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Snowflake, Cassandra, NoSQL, SQL, R, Scala, Optimization</t>
+          <t>Data Scientist, Docker, CI/CD, Git, Databricks, PySpark, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,42 +601,1932 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d75b05ba4615bbc0</t>
+          <t>https://www.indeed.com/viewjob?jk=86f8075b573654a6</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Oracle DBA - OCI</t>
+          <t>Software Engineer - SAP SuccessFactors</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Smithfield, RI, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Snowflake, Cassandra, NoSQL, SQL, R, Scala, Optimization</t>
+          <t>LangChain, RAG, Copilot, Prompt Engineering, CI/CD, Jenkins, GitHub Actions, Git, R, Java</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f2e0b0ce06ff46c4</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>AI Engineer</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>ETS</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Princeton, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Copilot, CI/CD, Git, Power BI, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
           <t>2026-03-19</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=03ea7797a2adda23</t>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b3338e1824b6591d</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Silicon Verification Infrastructure Engineer</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>10</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, CI/CD, Jenkins, Git, MySQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=638ed017602f1a84</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer - Generative AI &amp; Full-Stack Applications</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Nashville, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>10</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, Generative AI, RAG, Kubernetes, CI/CD, Git, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a9566bdb288c7be2</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer - Generative AI &amp; Full-Stack Applications</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Des Moines, IA, US USA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>10</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, Generative AI, RAG, Kubernetes, CI/CD, Git, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=09e740cc822f27d8</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer - Generative AI &amp; Full-Stack Applications</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Providence, RI, US USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>10</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, Generative AI, RAG, Kubernetes, CI/CD, Git, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=19943a1749f5eb10</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer - Generative AI &amp; Full-Stack Applications</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>10</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, Generative AI, RAG, Kubernetes, CI/CD, Git, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2b002210756636d3</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer - Generative AI &amp; Full-Stack Applications</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Charleston, WV, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>10</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, Generative AI, RAG, Kubernetes, CI/CD, Git, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=64bc5731f170baa6</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer - Generative AI &amp; Full-Stack Applications</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>10</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, Generative AI, RAG, Kubernetes, CI/CD, Git, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c27ca59aeb7d692f</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer - Generative AI &amp; Full-Stack Applications</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Sacramento, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>10</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, Generative AI, RAG, Kubernetes, CI/CD, Git, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=efb3b0417f856df4</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer - Generative AI &amp; Full-Stack Applications</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Dover, DE, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>10</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, Generative AI, RAG, Kubernetes, CI/CD, Git, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=49ad3c8a82595d5d</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer - Generative AI &amp; Full-Stack Applications</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Washington, DC, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>10</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, Generative AI, RAG, Kubernetes, CI/CD, Git, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=923ea9f1def1157f</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer - Generative AI &amp; Full-Stack Applications</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Augusta, ME, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>10</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, Generative AI, RAG, Kubernetes, CI/CD, Git, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bef60c3370a33e63</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer - Generative AI &amp; Full-Stack Applications</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Helena, MT, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>10</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, Generative AI, RAG, Kubernetes, CI/CD, Git, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b1ff8a9df30c9a2d</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer - Generative AI &amp; Full-Stack Applications</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>10</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, Generative AI, RAG, Kubernetes, CI/CD, Git, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d4f320e01bbcde10</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer - Generative AI &amp; Full-Stack Applications</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Springfield, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>10</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, Generative AI, RAG, Kubernetes, CI/CD, Git, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b33c6b32e4bcfc17</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer - Generative AI &amp; Full-Stack Applications</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Salem, OR, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>10</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, Generative AI, RAG, Kubernetes, CI/CD, Git, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9185433bb9295a64</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer - Generative AI &amp; Full-Stack Applications</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Cheyenne, WY, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>10</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, Generative AI, RAG, Kubernetes, CI/CD, Git, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9d2813b9c1f4a1a3</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer - Generative AI &amp; Full-Stack Applications</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Madison, WI, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, Generative AI, RAG, Kubernetes, CI/CD, Git, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fb7baa4f071bb506</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer - Generative AI &amp; Full-Stack Applications</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Santa Fe, NM, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>10</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, Generative AI, RAG, Kubernetes, CI/CD, Git, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=59a672b91ba76155</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer - Generative AI &amp; Full-Stack Applications</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Albany, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>10</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, Generative AI, RAG, Kubernetes, CI/CD, Git, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4eb0c7b6f4160a4e</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer - Generative AI &amp; Full-Stack Applications</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Olympia, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>10</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, Generative AI, RAG, Kubernetes, CI/CD, Git, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=017a48bdebaf233b</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer - Generative AI &amp; Full-Stack Applications</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Jackson, MS, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>10</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, Generative AI, RAG, Kubernetes, CI/CD, Git, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f001df5402760b32</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer - Generative AI &amp; Full-Stack Applications</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Trenton, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>10</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, Generative AI, RAG, Kubernetes, CI/CD, Git, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d279d089b4d8ae41</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer - Generative AI &amp; Full-Stack Applications</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>10</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, Generative AI, RAG, Kubernetes, CI/CD, Git, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5a469830a7acd8d2</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer - Generative AI &amp; Full-Stack Applications</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Columbia, SC, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>10</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, Generative AI, RAG, Kubernetes, CI/CD, Git, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=089e5845e8dc2d78</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer - Generative AI &amp; Full-Stack Applications</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Harrisburg, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>10</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, Generative AI, RAG, Kubernetes, CI/CD, Git, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cccf3dac15c4178b</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer - Generative AI &amp; Full-Stack Applications</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Saint Paul, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>10</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, Generative AI, RAG, Kubernetes, CI/CD, Git, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d4e5a2097527829d</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer - Generative AI &amp; Full-Stack Applications</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Oklahoma City, OK, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>10</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, Generative AI, RAG, Kubernetes, CI/CD, Git, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5fe631d50ec5be8e</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer - Generative AI &amp; Full-Stack Applications</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Phoenix, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>10</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, Generative AI, RAG, Kubernetes, CI/CD, Git, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=86cd457032c73fbf</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer - Generative AI &amp; Full-Stack Applications</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Carson City, NV, US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>10</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, Generative AI, RAG, Kubernetes, CI/CD, Git, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=653cd96c5af9f2fa</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer - Generative AI &amp; Full-Stack Applications</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Tallahassee, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>10</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, Generative AI, RAG, Kubernetes, CI/CD, Git, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e0aea96d4544e07a</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer - Generative AI &amp; Full-Stack Applications</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Richmond, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>10</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, Generative AI, RAG, Kubernetes, CI/CD, Git, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ab70424f0d089cd3</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer - Generative AI &amp; Full-Stack Applications</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Montpelier, VT, US USA</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>10</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, Generative AI, RAG, Kubernetes, CI/CD, Git, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=72e3bedd1dad63be</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer - Generative AI &amp; Full-Stack Applications</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Salt Lake City, UT, US USA</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>10</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, Generative AI, RAG, Kubernetes, CI/CD, Git, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=044b6a4291f23a69</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer - Generative AI &amp; Full-Stack Applications</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Topeka, KS, US USA</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>10</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, Generative AI, RAG, Kubernetes, CI/CD, Git, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c0e9b9c1faf5e5c9</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer - Generative AI &amp; Full-Stack Applications</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Frankfort, KY, US USA</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>10</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, Generative AI, RAG, Kubernetes, CI/CD, Git, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=882a278501b8e5f5</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer - Generative AI &amp; Full-Stack Applications</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Indianapolis, IN, US USA</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>10</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, Generative AI, RAG, Kubernetes, CI/CD, Git, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4f3f1367678b255c</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer - Generative AI &amp; Full-Stack Applications</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Honolulu, HI, US USA</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>10</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, Generative AI, RAG, Kubernetes, CI/CD, Git, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=853e17eba4c08c3a</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer - Generative AI &amp; Full-Stack Applications</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Hartford, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>10</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, Generative AI, RAG, Kubernetes, CI/CD, Git, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2b1073a150381121</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer - Generative AI &amp; Full-Stack Applications</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Raleigh, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>10</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, Generative AI, RAG, Kubernetes, CI/CD, Git, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e74feda0941e7bf7</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer - Generative AI &amp; Full-Stack Applications</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Annapolis, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>10</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, Generative AI, RAG, Kubernetes, CI/CD, Git, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=01c7a346e675ac19</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer - Generative AI &amp; Full-Stack Applications</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Bismarck, ND, US USA</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>10</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, Generative AI, RAG, Kubernetes, CI/CD, Git, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1be83753ec9ec17e</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer - Generative AI &amp; Full-Stack Applications</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Pierre, SD, US USA</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>10</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, Generative AI, RAG, Kubernetes, CI/CD, Git, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1fdc92fb91de10df</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer - Generative AI &amp; Full-Stack Applications</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Boise, ID, US USA</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>10</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, Generative AI, RAG, Kubernetes, CI/CD, Git, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bde97e48e43af4af</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer - Generative AI &amp; Full-Stack Applications</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Lansing, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>10</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, Generative AI, RAG, Kubernetes, CI/CD, Git, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f33e053ff6e7e94e</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer - Generative AI &amp; Full-Stack Applications</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Montgomery, AL, US USA</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>10</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, Generative AI, RAG, Kubernetes, CI/CD, Git, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=443c7dd8f3df90c0</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer - Generative AI &amp; Full-Stack Applications</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Baton Rouge, LA, US USA</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>10</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, Generative AI, RAG, Kubernetes, CI/CD, Git, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=281286c2cddab92c</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer - Generative AI &amp; Full-Stack Applications</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Concord, NH, US USA</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>10</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, Generative AI, RAG, Kubernetes, CI/CD, Git, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cd9de4c416f93915</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer - Generative AI &amp; Full-Stack Applications</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Little Rock, AR, US USA</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>10</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, Generative AI, RAG, Kubernetes, CI/CD, Git, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9866f9221f7870c6</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer - Generative AI &amp; Full-Stack Applications</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Juneau, AK, US USA</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>10</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, Generative AI, RAG, Kubernetes, CI/CD, Git, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3b002ee2168180be</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer - Generative AI &amp; Full-Stack Applications</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Lincoln, NE, US USA</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>10</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, Generative AI, RAG, Kubernetes, CI/CD, Git, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5d8adcaeda26da83</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer - Generative AI &amp; Full-Stack Applications</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Jefferson City, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>10</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, Generative AI, RAG, Kubernetes, CI/CD, Git, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=73fbe0f0b36d2bb0</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer - Generative AI &amp; Full-Stack Applications</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>10</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, Generative AI, RAG, Kubernetes, CI/CD, Git, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5a9d82e65d688d59</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Sr Software Engineer, Enterprise GenAI</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Adobe</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>10</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Docker, CI/CD, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b6c0ce6c3f399b24</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-03-20.xlsx
+++ b/daily_matches/job_matches_2026-03-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SAP AI Business Services Consultant</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Bradenton, FL, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>20</v>
+        <v>16.7</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Pinecone, Prompt Engineering, TensorFlow, PyTorch, MLflow</t>
+          <t>Generative AI, LangChain, RAG, LLaMA, Gemini, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Keras</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f69b370f0270ee30</t>
+          <t>https://www.indeed.com/viewjob?jk=80035acec713050b</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SAP AI Business Services Consultant</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Zoom Communications</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>17.8</v>
+        <v>12.2</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, FastAPI, Docker</t>
+          <t>S3, EC2, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,462 +531,42 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afd140f81b2a4813</t>
+          <t>https://www.indeed.com/viewjob?jk=f933ed4a7abbea6e</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>WorldPac</t>
+          <t>Detroit Tigers</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>17.8</v>
+        <v>10</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, Copilot, FAISS, Pinecone, Prompt Engineering, FastAPI, CI/CD</t>
+          <t>Data Scientist, RAG, Data Lake, CI/CD, Databricks, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdb05ecb3a99348f</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>SAP AI Business Services Consultant</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, Prompt Engineering, TensorFlow, PyTorch, FastAPI, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=684c3d291a04beb2</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>SAP AI Business Services Consultant</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>RAG, Prompt Engineering, TensorFlow, PyTorch, S3, EC2, Docker, Kubernetes, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5f3bab5f2ccae161</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Associate Software Engineer - Agentic AI Framework (Python, AWS)</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Gartner</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Irving, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Prompt Engineering, S3, EC2, Glue, Redshift, Docker, Kubernetes, CI/CD, Redshift, PostgreSQL</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0f067cb08ee5b102</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>AWS Engineer - Contract</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Navat Technologies Pvt Ltd</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Riverwoods, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>RAG, Gemini, EC2, Redshift, Docker, CI/CD, Jenkins, Terraform, Redshift, PostgreSQL</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=13f06a9a34997131</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Programmer Analyst, Senior</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Pacific Gas and Electric</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Oakland, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>RAG, S3, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, PostgreSQL, Python</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=39cbab5132d19231</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Cloud DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Gen II Fund Services</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Docker, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=38a5ed1c6ce89902</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Cloud Data Engineer</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Barclays</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Whippany, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, S3, EC2, Glue, Data Lake, CI/CD, Git, Kafka, R</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bf20edf4b871568c</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Sr Data Scientist</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>MidAmerican Energy</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Des Moines, IA, US USA</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, Data Lake, Databricks, PySpark, Power BI, Seaborn, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1ba5b75525859680</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Sr Software Engineer - Media Platform Alliance</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, S3, Kubernetes, Kafka, PostgreSQL, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1db4cfb36c2bb000</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Data Architect - Data Lake &amp; Data Engineering</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Chevron</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Houston, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>10</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>RAG, Data Lake, CI/CD, Databricks, PySpark, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a2dd3db330a009de</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Cloudera</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>GA, US USA</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>10</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, Git, Hadoop, SQL, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5cddaebc2ffa2275</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>SAP AI Business Services Consultant</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>10</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>RAG, Hugging Face, TensorFlow, PyTorch, Keras, spaCy, FastAPI, Python, R</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=697aeeac62b7c85e</t>
+          <t>https://www.indeed.com/viewjob?jk=bb65c2bedee3ee63</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-03-20.xlsx
+++ b/daily_matches/job_matches_2026-03-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,105 +468,455 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Junior AI/ML Engineer (Data &amp; Cloud Platforms)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Mod Op</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Bradenton, FL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16.7</v>
+        <v>20</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, LLaMA, Gemini, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Keras</t>
+          <t>Data Scientist, AWS SageMaker, GCP Vertex AI, Azure ML, Redshift, BigQuery, Synapse, Dataflow, Snowflake, BigQuery</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80035acec713050b</t>
+          <t>https://www.indeed.com/viewjob?jk=d1204728c106ec46</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Zoom Communications</t>
+          <t>Micron Technology</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>12.2</v>
+        <v>20</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>S3, EC2, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R</t>
+          <t>Machine Learning Engineer, Generative AI, RAG, TensorFlow, PyTorch, Dataflow, Docker, Kubernetes, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f933ed4a7abbea6e</t>
+          <t>https://www.indeed.com/viewjob?jk=9d2163f01dd05b34</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>Senior Data Engineer – CDO / Data &amp; AI Engineering</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Detroit Tigers</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, LangChain, RAG, Synapse, Data Lake, CI/CD, Jenkins, Git, Snowflake</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c03da34050d1fb85</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer (Remote, US)</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Openly</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, BigQuery, Kubernetes, CI/CD, Terraform, Git, BigQuery, Kafka, PostgreSQL</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4d18e2b948851633</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Senior Solution Architect</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Bain &amp; Company</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>RAG, Redshift, Docker, Kubernetes, Redshift, Kafka, MongoDB, Cassandra, NoSQL, Python</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dfa0447b668a6f99</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Developer Services</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>T. Rowe Price</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Owings Mills, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, RAG, S3, Docker, CI/CD, Terraform, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8c256a34f180680f</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>AI Intern</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>GAF</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Parsippany-Troy Hills, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, Prompt Engineering, TensorFlow, PyTorch, Git, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ada66138b8ffdc45</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Enterprise AI Architect</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, RAG, TensorFlow, Kubernetes, CI/CD, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5836f25d118ca699</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Enterprise AI Architect</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, RAG, TensorFlow, Kubernetes, CI/CD, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b0a4fd9c5e503629</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Eden Prairie, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
         <v>10</v>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, Data Lake, CI/CD, Databricks, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, MySQL, NoSQL, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
         <is>
           <t>2026-03-20</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bb65c2bedee3ee63</t>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=74fd1f39f284ae52</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Micron Technology</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Boise, ID, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>10</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, CI/CD, Git, Hadoop, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f6c3bde19973947c</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>AI Solutions Specialist- Fully Remote Opportunity</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Answer Financial Inc.</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Encino, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>10</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Generative AI, LLaMA, Gemini, Copilot, Python, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f161ddbce2d4819a</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>AI Solutions Specialist- Fully Remote Opportunity</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Answer Financial Inc.</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Knoxville, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>10</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Generative AI, LLaMA, Gemini, Copilot, Python, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5555c5815191d158</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-03-20.xlsx
+++ b/daily_matches/job_matches_2026-03-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,17 +468,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Junior AI/ML Engineer (Data &amp; Cloud Platforms)</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Mod Op</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -486,77 +486,77 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, AWS SageMaker, GCP Vertex AI, Azure ML, Redshift, BigQuery, Synapse, Dataflow, Snowflake, BigQuery</t>
+          <t>Machine Learning Engineer, Generative AI, LangChain, RAG, Copilot, MLflow, Docker, Kubernetes, CI/CD, Git</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1204728c106ec46</t>
+          <t>https://www.indeed.com/viewjob?jk=1fecb0cbc521360f</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Micron Technology</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>20</v>
+        <v>17.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Generative AI, RAG, TensorFlow, PyTorch, Dataflow, Docker, Kubernetes, CI/CD, Jenkins</t>
+          <t>LangChain, RAG, Copilot, FastAPI, Docker, Kubernetes, CI/CD, Git, Snowflake, Databricks</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d2163f01dd05b34</t>
+          <t>https://www.indeed.com/viewjob?jk=c929b0d5d0c4abe8</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – CDO / Data &amp; AI Engineering</t>
+          <t>Senior Solution Architect</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Bain &amp; Company</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.9</v>
+        <v>15.6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, LangChain, RAG, Synapse, Data Lake, CI/CD, Jenkins, Git, Snowflake</t>
+          <t>RAG, Redshift, Docker, Kubernetes, Redshift, Kafka, MongoDB, Cassandra, NoSQL, Python</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c03da34050d1fb85</t>
+          <t>https://www.indeed.com/viewjob?jk=20bcf9c2d03f083c</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Remote, US)</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Openly</t>
+          <t>TherapyNotes</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16.7</v>
+        <v>14.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, Copilot, BigQuery, Kubernetes, CI/CD, Terraform, Git, BigQuery, Kafka, PostgreSQL</t>
+          <t>LangChain, RAG, Gemini, Copilot, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,59 +601,59 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d18e2b948851633</t>
+          <t>https://www.indeed.com/viewjob?jk=74fea87b2950bcd4</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Solution Architect</t>
+          <t>Senior Software Engineer - Middleware/Integration</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Bain &amp; Company</t>
+          <t>STAND TOGETHER</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, Redshift, Docker, Kubernetes, Redshift, Kafka, MongoDB, Cassandra, NoSQL, Python</t>
+          <t>RAG, S3, Docker, CI/CD, GitHub Actions, Terraform, Git, MongoDB, NoSQL, SQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfa0447b668a6f99</t>
+          <t>https://www.indeed.com/viewjob?jk=c38431e7f505eb9d</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Developer Services</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>T. Rowe Price</t>
+          <t>Eli Lilly</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Owings Mills, MD, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, S3, Docker, CI/CD, Terraform, Git, Python, R</t>
+          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, S3, Databricks, Python, R, Optimization, Bayesian</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c256a34f180680f</t>
+          <t>https://www.indeed.com/viewjob?jk=ffa8b913c8fc8798</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AI Intern</t>
+          <t>Associate AI Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>GAF</t>
+          <t>Columbia University</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Parsippany-Troy Hills, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, Prompt Engineering, TensorFlow, PyTorch, Git, Python, SQL, R</t>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, LLaMA, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ada66138b8ffdc45</t>
+          <t>https://www.indeed.com/viewjob?jk=72689e7db12f93f3</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Enterprise AI Architect</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Tensley Consulting, Inc.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Annapolis Junction, MD, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, RAG, TensorFlow, Kubernetes, CI/CD, Git, Python, R, Scala</t>
+          <t>RAG, Docker, Kubernetes, Git, Kafka, PostgreSQL, MongoDB, Python, SQL, R</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5836f25d118ca699</t>
+          <t>https://www.indeed.com/viewjob?jk=ebcfd38ee6fef503</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Enterprise AI Architect</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Albertsons</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Pleasanton, CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, RAG, TensorFlow, Kubernetes, CI/CD, Git, Python, R, Scala</t>
+          <t>Data Scientist, RAG, Git, Snowflake, Databricks, Hadoop, Python, SQL, R, Optimization</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0a4fd9c5e503629</t>
+          <t>https://www.indeed.com/viewjob?jk=e75930b96a9894ad</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>DevOps/Platform Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, MySQL, NoSQL, Python, SQL, R, Java, Scala</t>
+          <t>Docker, Kubernetes, AKS, CI/CD, Jenkins, Terraform, Git, Snowflake, Databricks, Python</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,112 +811,182 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74fd1f39f284ae52</t>
+          <t>https://www.indeed.com/viewjob?jk=ad34594ef5800a70</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Data Engineer (ETL/SQL)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Micron Technology</t>
+          <t>FULLTHROTTLE</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, CI/CD, Git, Hadoop, Python, SQL, R, Optimization</t>
+          <t>TensorFlow, PyTorch, Keras, spaCy, NLTK, OpenCV, S3, Python, SQL, R</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6c3bde19973947c</t>
+          <t>https://www.indeed.com/viewjob?jk=6297519625ee3c87</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AI Solutions Specialist- Fully Remote Opportunity</t>
+          <t>Agent Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Answer Financial Inc.</t>
+          <t>Scotts Miracle-Gro</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Encino, CA, US USA</t>
+          <t>Marysville, OH, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Generative AI, LLaMA, Gemini, Copilot, Python, R, Java, Scala, Optimization</t>
+          <t>Generative AI, LangChain, RAG, Gemini, Prompt Engineering, CI/CD, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f161ddbce2d4819a</t>
+          <t>https://www.indeed.com/viewjob?jk=5279d8a60d0a7b5c</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AI Solutions Specialist- Fully Remote Opportunity</t>
+          <t>Sr. Software Engineer, Java Full Stack</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Answer Financial Inc.</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Knoxville, TN, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>RAG, S3, CI/CD, Git, Kafka, NoSQL, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8cdca05a9ea0e87f</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Agentic AI Developer</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Infosys</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
         <v>10</v>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Generative AI, LLaMA, Gemini, Copilot, Python, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>2026-03-08</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5555c5815191d158</t>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, LangChain, Gemini, TensorFlow, PyTorch, Python, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c7c4e73ead832b83</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Intern, Data Science (Sporting)</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>St. Louis City SC</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>St. Louis, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>10</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Tableau, Power BI, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=85931423a1f91582</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-03-20.xlsx
+++ b/daily_matches/job_matches_2026-03-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,17 +468,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>AI Engineer Senior</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>Texas Capital Bank</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -486,24 +486,24 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Generative AI, LangChain, RAG, Copilot, MLflow, Docker, Kubernetes, CI/CD, Git</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Pinecone, Prompt Engineering, Docker, Kubernetes, CI/CD</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fecb0cbc521360f</t>
+          <t>https://www.indeed.com/viewjob?jk=9e394b0856792b66</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>AI Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -513,50 +513,50 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Doral, FL, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>17.8</v>
+        <v>18.9</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Copilot, FastAPI, Docker, Kubernetes, CI/CD, Git, Snowflake, Databricks</t>
+          <t>Machine Learning Engineer, RAG, Copilot, Prompt Engineering, TensorFlow, Synapse, Data Lake, FastAPI, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c929b0d5d0c4abe8</t>
+          <t>https://www.indeed.com/viewjob?jk=bb98bc0da3b1f6fd</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Solution Architect</t>
+          <t>Gen AI Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Bain &amp; Company</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15.6</v>
+        <v>17.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, Redshift, Docker, Kubernetes, Redshift, Kafka, MongoDB, Cassandra, NoSQL, Python</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Gemini, Hugging Face, Prompt Engineering, TensorFlow, PyTorch</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20bcf9c2d03f083c</t>
+          <t>https://www.indeed.com/viewjob?jk=700cbfaab697918f</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>TherapyNotes</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Bradenton, FL, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14.4</v>
+        <v>16.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Gemini, Copilot, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git</t>
+          <t>Generative AI, LangChain, RAG, LLaMA, Gemini, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Keras</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74fea87b2950bcd4</t>
+          <t>https://www.indeed.com/viewjob?jk=8d101f0f85886045</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Middleware/Integration</t>
+          <t>Text and Speech Analyst</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>STAND TOGETHER</t>
+          <t>Arbitration Forums Inc.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, S3, Docker, CI/CD, GitHub Actions, Terraform, Git, MongoDB, NoSQL, SQL</t>
+          <t>Data Scientist, Cortex, TensorFlow, PyTorch, Keras, Azure ML, Git, Snowflake, Databricks, Power BI</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,94 +636,94 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c38431e7f505eb9d</t>
+          <t>https://www.indeed.com/viewjob?jk=8c8d97239a690028</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Computer Vision Data Scientist</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Eli Lilly</t>
+          <t>ProVation</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, S3, Databricks, Python, R, Optimization, Bayesian</t>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, TensorFlow, PyTorch, OpenCV, CI/CD, Python, SQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffa8b913c8fc8798</t>
+          <t>https://www.indeed.com/viewjob?jk=09016959bae6c36d</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Associate AI Engineer</t>
+          <t>Computer Vision Data Scientist</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Columbia University</t>
+          <t>ProVation</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, LLaMA, Git, Python, R, Java</t>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, TensorFlow, PyTorch, OpenCV, CI/CD, Python, SQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72689e7db12f93f3</t>
+          <t>https://www.indeed.com/viewjob?jk=dc0db03a5463b6c7</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Security Engineer II – Cloud &amp; Data Security</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Tensley Consulting, Inc.</t>
+          <t>Sigma Computing</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Annapolis Junction, MD, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, Git, Kafka, PostgreSQL, MongoDB, Python, SQL, R</t>
+          <t>RAG, BigQuery, Kubernetes, CI/CD, Terraform, Snowflake, Databricks, BigQuery, Python, SQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebcfd38ee6fef503</t>
+          <t>https://www.indeed.com/viewjob?jk=fe3338ab667344c2</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Technical Support Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Albertsons</t>
+          <t>Sigma Computing</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Pleasanton, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Git, Snowflake, Databricks, Hadoop, Python, SQL, R, Optimization</t>
+          <t>RAG, Redshift, BigQuery, Snowflake, Databricks, BigQuery, Redshift, Python, SQL, R</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e75930b96a9894ad</t>
+          <t>https://www.indeed.com/viewjob?jk=4c34e89d42bb3ebd</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>DevOps/Platform Engineer</t>
+          <t>Marketing Data Scientist</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>webuyanycar.com</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Springfield, PA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, AKS, CI/CD, Jenkins, Terraform, Git, Snowflake, Databricks, Python</t>
+          <t>Data Scientist, TensorFlow, Hadoop, Tableau, Power BI, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad34594ef5800a70</t>
+          <t>https://www.indeed.com/viewjob?jk=a838d169299fd142</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer (ETL/SQL)</t>
+          <t>Technical Support Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>FULLTHROTTLE</t>
+          <t>Sigma Computing</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>TensorFlow, PyTorch, Keras, spaCy, NLTK, OpenCV, S3, Python, SQL, R</t>
+          <t>RAG, Redshift, BigQuery, Snowflake, BigQuery, Redshift, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6297519625ee3c87</t>
+          <t>https://www.indeed.com/viewjob?jk=c06cebc7b22a9bd1</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Agent Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Scotts Miracle-Gro</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Marysville, OH, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, Gemini, Prompt Engineering, CI/CD, Git, Python, R, Java</t>
+          <t>RAG, CI/CD, MySQL, NoSQL, Python, SQL, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5279d8a60d0a7b5c</t>
+          <t>https://www.indeed.com/viewjob?jk=fa146328f582d2ee</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, Java Full Stack</t>
+          <t>Software Automation Engineer (GSGT)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Fluke</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Everett, WA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,34 +906,34 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, S3, CI/CD, Git, Kafka, NoSQL, SQL, R, Java, Scala</t>
+          <t>RAG, Data Lake, Git, NoSQL, Python, SQL, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cdca05a9ea0e87f</t>
+          <t>https://www.indeed.com/viewjob?jk=1280584c5f5d3242</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Agentic AI Developer</t>
+          <t>GEN AI Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Infosys</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, Gemini, TensorFlow, PyTorch, Python, R, Optimization</t>
+          <t>AI Engineer, LangChain, RAG, Prompt Engineering, Python, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7c4e73ead832b83</t>
+          <t>https://www.indeed.com/viewjob?jk=f0c678b7b447c879</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Intern, Data Science (Sporting)</t>
+          <t>Fullstack Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>St. Louis City SC</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Tableau, Power BI, Python, SQL, R, Scala, Optimization</t>
+          <t>CI/CD, MongoDB, NoSQL, Python, SQL, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,7 +986,77 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85931423a1f91582</t>
+          <t>https://www.indeed.com/viewjob?jk=7ea1aa636d52969f</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Senior Technical Data Analyst - Operations E2E Data Intelligent Systems</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>NVIDIA</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Santa Clara, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>10</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Data Lake, Snowflake, Databricks, PySpark, Tableau, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1d98b800fce8aaa0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>APIGEE Development Engineer</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>NTT DATA</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Morris Plains, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>10</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Docker, Kubernetes, CI/CD, Jenkins, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0f865d350c566772</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-03-20.xlsx
+++ b/daily_matches/job_matches_2026-03-20.xlsx
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AI Engineer Senior</t>
+          <t>Sr. GenAI Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Texas Capital Bank</t>
+          <t>Skechers</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Manhattan Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>20</v>
+        <v>23.3</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Pinecone, Prompt Engineering, Docker, Kubernetes, CI/CD</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Prompt Engineering, S3, EC2, FastAPI, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,67 +496,67 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e394b0856792b66</t>
+          <t>https://www.indeed.com/viewjob?jk=5f37a180376834e2</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AI Machine Learning Engineer</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Doral, FL, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.9</v>
+        <v>21.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, RAG, Copilot, Prompt Engineering, TensorFlow, Synapse, Data Lake, FastAPI, Kubernetes, AKS</t>
+          <t>RAG, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, OpenCV, Docker, Kubernetes, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb98bc0da3b1f6fd</t>
+          <t>https://www.indeed.com/viewjob?jk=93cc54a6ab2b9aba</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Gen AI Engineer</t>
+          <t>Software Engineer III (SWES03) DT_AI/ML</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>17.8</v>
+        <v>18.9</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Gemini, Hugging Face, Prompt Engineering, TensorFlow, PyTorch</t>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, AWS SageMaker, Azure ML, Docker, Kubernetes, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=700cbfaab697918f</t>
+          <t>https://www.indeed.com/viewjob?jk=1194dbf1a39e9b3e</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Software Engineer II_AI/ML</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Bradenton, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16.7</v>
+        <v>17.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, LLaMA, Gemini, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Keras</t>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, AWS SageMaker, Azure ML, Docker, Kubernetes, CI/CD, Git</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d101f0f85886045</t>
+          <t>https://www.indeed.com/viewjob?jk=e5f638e48249099e</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Text and Speech Analyst</t>
+          <t>Software Engineer II - Enterprise AI Products</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Arbitration Forums Inc.</t>
+          <t>Travelers</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>15.6</v>
+        <v>17.8</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Data Scientist, Cortex, TensorFlow, PyTorch, Keras, Azure ML, Git, Snowflake, Databricks, Power BI</t>
+          <t>RAG, Prompt Engineering, Kubernetes, AKS, CI/CD, Jenkins, GitHub Actions, Terraform, Git, MongoDB</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c8d97239a690028</t>
+          <t>https://www.indeed.com/viewjob?jk=67984d7d68bde23e</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Computer Vision Data Scientist</t>
+          <t>Senior Java Python Full Stack Developer -Software Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ProVation</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,34 +661,34 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, TensorFlow, PyTorch, OpenCV, CI/CD, Python, SQL</t>
+          <t>Generative AI, RAG, Gemini, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09016959bae6c36d</t>
+          <t>https://www.indeed.com/viewjob?jk=688358c2a9b02664</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Computer Vision Data Scientist</t>
+          <t>Java Python Full Stack Developer Associate Software Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ProVation</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,42 +696,42 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, TensorFlow, PyTorch, OpenCV, CI/CD, Python, SQL</t>
+          <t>Generative AI, RAG, Gemini, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc0db03a5463b6c7</t>
+          <t>https://www.indeed.com/viewjob?jk=80c25592f9425b10</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Security Engineer II – Cloud &amp; Data Security</t>
+          <t>Java Python Full Stack Developer - Associate Software Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Sigma Computing</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Kubernetes, CI/CD, Terraform, Snowflake, Databricks, BigQuery, Python, SQL</t>
+          <t>Generative AI, RAG, Gemini, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe3338ab667344c2</t>
+          <t>https://www.indeed.com/viewjob?jk=5b6bab89238cc7fe</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Technical Support Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Sigma Computing</t>
+          <t>BAE Systems USA</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, Redshift, BigQuery, Snowflake, Databricks, BigQuery, Redshift, Python, SQL, R</t>
+          <t>RAG, Redshift, BigQuery, Snowflake, BigQuery, Redshift, Kafka, Hadoop, Matplotlib, Seaborn</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c34e89d42bb3ebd</t>
+          <t>https://www.indeed.com/viewjob?jk=0f215a50593a8ff4</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Marketing Data Scientist</t>
+          <t>Kubernetes Application Support Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>webuyanycar.com</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Springfield, PA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Data Scientist, TensorFlow, Hadoop, Tableau, Power BI, Python, SQL, R, Scala, Optimization</t>
+          <t>Generative AI, RAG, Gemini, Docker, Kubernetes, AKS, Jenkins, GitHub Actions, Terraform, Git</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a838d169299fd142</t>
+          <t>https://www.indeed.com/viewjob?jk=2f4d370935d2701d</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Technical Support Engineer</t>
+          <t>Generative AI Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Sigma Computing</t>
+          <t>NeuroHire</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>California City, CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, Redshift, BigQuery, Snowflake, BigQuery, Redshift, Python, SQL, R, Scala</t>
+          <t>AI Engineer, Generative AI, RAG, TensorFlow, Hadoop, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c06cebc7b22a9bd1</t>
+          <t>https://www.indeed.com/viewjob?jk=df45123688a8961e</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Java Developer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, MySQL, NoSQL, Python, SQL, R, Java, Scala, Optimization</t>
+          <t>Generative AI, RAG, Gemini, Docker, Kubernetes, Git, Kafka, SQL, R, Java</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,67 +881,67 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa146328f582d2ee</t>
+          <t>https://www.indeed.com/viewjob?jk=a0d3a6d0feeb2ba8</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Software Automation Engineer (GSGT)</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Fluke</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Everett, WA, US USA</t>
+          <t>Menlo Park, CA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, Data Lake, Git, NoSQL, Python, SQL, R, Java, Scala, Optimization</t>
+          <t>Data Scientist, Redshift, BigQuery, Snowflake, BigQuery, Redshift, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1280584c5f5d3242</t>
+          <t>https://www.indeed.com/viewjob?jk=4a47e0aee2cf453c</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>GEN AI Engineer</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>La Mesa RV Center</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, Prompt Engineering, Python, R, Java, Scala, Optimization</t>
+          <t>RAG, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Databricks, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0c678b7b447c879</t>
+          <t>https://www.indeed.com/viewjob?jk=7e48f0e2e494934e</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Fullstack Engineer</t>
+          <t>AI Engineering Intern</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Littelfuse</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>CI/CD, MongoDB, NoSQL, Python, SQL, R, Java, Scala, Optimization</t>
+          <t>AI Engineer, RAG, Prompt Engineering, FastAPI, Docker, Git, PostgreSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ea1aa636d52969f</t>
+          <t>https://www.indeed.com/viewjob?jk=b1cac52596561dd8</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Technical Data Analyst - Operations E2E Data Intelligent Systems</t>
+          <t>Capgemini Invent - AI Solutions Architecture &amp; Engineering Consultant</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Data Lake, Snowflake, Databricks, PySpark, Tableau, Python, SQL, R, Scala</t>
+          <t>AI Engineer, Generative AI, RAG, Gemini, Git, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d98b800fce8aaa0</t>
+          <t>https://www.indeed.com/viewjob?jk=cfd9a8523768c24f</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>APIGEE Development Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Arch Telecom</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Morris Plains, NJ, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, CI/CD, Jenkins, Git, Python, R, Java, Scala</t>
+          <t>AI Engineer, Generative AI, TensorFlow, PyTorch, Git, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f865d350c566772</t>
+          <t>https://www.indeed.com/viewjob?jk=dd872d327ee5725d</t>
         </is>
       </c>
     </row>
